--- a/ExportedReports/Tasks_Elena_Rostova_Only.xlsx
+++ b/ExportedReports/Tasks_Elena_Rostova_Only.xlsx
@@ -19,7 +19,7 @@
     <x:t>Task Management System — Export Report</x:t>
   </x:si>
   <x:si>
-    <x:t>Filters: User: Elena Rostova | Exported: 2026-10-21 02:32 UTC | Total: 5</x:t>
+    <x:t>Filters: User: Elena Rostova | Exported: 2026-10-21 05:50 AM (Egypt Time) | Total: 5</x:t>
   </x:si>
   <x:si>
     <x:t>Task #</x:t>
@@ -46,46 +46,46 @@
     <x:t>elena.rostova@tasksystem.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-20 20:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-20 21:32</x:t>
+    <x:t>2026-10-20 11:32 PM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-21 12:32 AM</x:t>
   </x:si>
   <x:si>
     <x:t>[Excel Export with ClosedXML] Architected high-performance Excel report builder utilizing ClosedXML. Added alternating row fills, thin gray borders, title banner, and streaming download response.</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-18 02:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-18 03:32</x:t>
+    <x:t>2026-10-18 05:32 AM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-18 06:32 AM</x:t>
   </x:si>
   <x:si>
     <x:t>[Dynamic Query Filtering Engine] Implemented reusable repository expressions to dynamically filter task submissions by timeframe preset (week/month/year) and explicit start/end dates.</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-09 02:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-09 03:02</x:t>
+    <x:t>2026-10-09 05:32 AM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-09 06:02 AM</x:t>
   </x:si>
   <x:si>
     <x:t>[SQL Index Optimization] Analyzed execution plans on Tasks table. Added B-Tree composite indices on (UserId) and (TaskDate) to ensure millisecond queries over millions of records.</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-26 02:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-26 04:32</x:t>
+    <x:t>2026-09-26 05:32 AM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-26 07:32 AM</x:t>
   </x:si>
   <x:si>
     <x:t>[Dual Authentication Pipeline] Configured ASP.NET Core middleware to simultaneously support JWT Bearer tokens for mobile clients and Cookie sessions for web admin dashboard.</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-03 02:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-03 06:32</x:t>
+    <x:t>2026-06-03 05:32 AM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-03 09:32 AM</x:t>
   </x:si>
   <x:si>
     <x:t>[Database Migration &amp; Seed Script] Constructed Entity Framework Core Code-First migrations and automated DB initializer with role management and admin provisioning.</x:t>
@@ -619,7 +619,8 @@
   <x:cols>
     <x:col min="1" max="1" width="10.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="24.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="5" width="28.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="5" width="30.710625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="50.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
